--- a/Project_ETF/ETF_Investment_Portfolio/0056/ETF_Investment_Portfolio_20260731.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0056/ETF_Investment_Portfolio_20260731.xlsx
@@ -1217,17 +1217,17 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>5876</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>上海商銀</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>160,155,041</t>
+          <t>218,959,713</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1239,17 +1239,17 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>5876</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>上海商銀</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>218,959,713</t>
+          <t>160,155,041</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1591,17 +1591,17 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>群光</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>22,845,826</t>
+          <t>33,055,453</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -1613,17 +1613,17 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>群光</t>
+          <t>中興電</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>33,055,453</t>
+          <t>22,845,826</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
